--- a/ExperimentsRecord.xlsx
+++ b/ExperimentsRecord.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\TerahertzCode\Terahertz\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70180199-A24F-4ADC-9F5E-BB9B715402FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-23805" yWindow="3705" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,114 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+  <si>
+    <t>名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline_4F_SmallRestormer_v2_0728</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>說明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3ONN_4F_SmallRestormer_v1_0730</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PSNR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSIM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用全隨機ONN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline_4F_SmallRestormer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w/o ONN, w/ 4F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修正crop與simulation沒有非常對齊的問題</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crop與simulation沒有非常對齊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99/100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optical 架構說明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>num_blocks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embed_dim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline_4F_SmallRestormer_v1_0802</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vaccination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Best/Total(epoch) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>51/73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNN 架構</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>閹割版Restormer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +139,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,11 +185,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +472,155 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="3" width="41.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5">
+        <v>4.5100000000000001E-4</v>
+      </c>
+      <c r="N5">
+        <v>33.460099999999997</v>
+      </c>
+      <c r="O5">
+        <v>0.98609999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6">
+        <v>3.9050000000000001E-3</v>
+      </c>
+      <c r="N6">
+        <v>24.0838</v>
+      </c>
+      <c r="O6">
+        <v>0.93279999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ExperimentsRecord.xlsx
+++ b/ExperimentsRecord.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\TerahertzCode\Terahertz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70180199-A24F-4ADC-9F5E-BB9B715402FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A52588C1-39D2-41E2-8989-32E419CC5A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23805" yWindow="3705" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,16 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Baseline_4F_SmallRestormer_v2_0728</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>說明</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -59,14 +56,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>使用全隨機ONN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Baseline_4F_SmallRestormer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w/o ONN, w/ 4F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -75,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>crop與simulation沒有非常對齊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>99/100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,10 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>embed_dim</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Baseline_4F_SmallRestormer_v1_0802</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -123,7 +104,67 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>閹割版Restormer</t>
+    <t>Baseline_4F_Restormer8_v1_0809</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,6,6,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>144/168</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pixel size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150um</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250um</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Refinement_blocks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline_4F_Restormer16_v1_0809</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline_4F_Restormer16_v2_0810</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Best_model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>last_model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simplified Restormer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iteration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parameters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 random ONN, w/ 4F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -185,12 +226,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -473,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -481,95 +525,108 @@
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" customWidth="1"/>
     <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
+      <c r="H1" s="4"/>
       <c r="I1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="Q1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" t="s">
         <v>4</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O2" t="s">
         <v>5</v>
       </c>
-      <c r="O1" t="s">
-        <v>6</v>
+      <c r="Q2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E2" t="s">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" t="s">
+        <v>9</v>
       </c>
       <c r="M5">
         <v>4.5100000000000001E-4</v>
@@ -581,30 +638,33 @@
         <v>0.98609999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
       </c>
       <c r="M6">
         <v>3.9050000000000001E-3</v>
@@ -616,9 +676,89 @@
         <v>0.93279999999999996</v>
       </c>
     </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>300000</v>
+      </c>
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7">
+        <v>9.0899999999999998E-4</v>
+      </c>
+      <c r="N7">
+        <v>30.412199999999999</v>
+      </c>
+      <c r="O7">
+        <v>0.97929999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E1:G1"/>
+  <mergeCells count="3">
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExperimentsRecord.xlsx
+++ b/ExperimentsRecord.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\TerahertzCode\Terahertz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A52588C1-39D2-41E2-8989-32E419CC5A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DC7F1D-4B8A-4246-8C2C-AB83F12132E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22500" yWindow="3000" windowWidth="21030" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
   <si>
     <t>名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,30 +115,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pixel size</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>150um</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>250um</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Refinement_blocks</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Baseline_4F_Restormer16_v1_0809</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Baseline_4F_Restormer16_v2_0810</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Best_model</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,15 +135,67 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Parameters</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3 random ONN, w/ 4F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensor Layer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Noise adder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ONN_Restormer8_v1_0824</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parameters(total/trainable)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parameters(ONN+DNN)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>166/168</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pixel size / ONN pixel =&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150um / 5*5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250um / 3*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test on 250um</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restormer_ONN16SBlock_v1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>168/168</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -226,11 +257,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -517,19 +551,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="3" width="41.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" customWidth="1"/>
+    <col min="2" max="4" width="41.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" customWidth="1"/>
+    <col min="11" max="11" width="25" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,106 +576,153 @@
       <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" t="s">
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="4"/>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="J1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="5" t="s">
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="Q1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T2" t="s">
+        <v>4</v>
+      </c>
+      <c r="U2" t="s">
+        <v>5</v>
+      </c>
+      <c r="V2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W2" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R2" t="s">
-        <v>4</v>
-      </c>
-      <c r="S2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5">
+        <v>36</v>
+      </c>
+      <c r="E5">
+        <v>49152</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>17</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" t="s">
         <v>9</v>
       </c>
-      <c r="M5">
+      <c r="P5">
         <v>4.5100000000000001E-4</v>
       </c>
-      <c r="N5">
+      <c r="Q5">
         <v>33.460099999999997</v>
       </c>
-      <c r="O5">
+      <c r="R5">
         <v>0.98609999999999998</v>
       </c>
+      <c r="S5">
+        <v>171.881621</v>
+      </c>
+      <c r="T5">
+        <v>-22.3523</v>
+      </c>
+      <c r="U5">
+        <v>0.33050000000000002</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -649,34 +733,52 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6">
+        <v>36</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6">
         <v>16</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>17</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" t="s">
         <v>16</v>
       </c>
-      <c r="M6">
+      <c r="P6">
         <v>3.9050000000000001E-3</v>
       </c>
-      <c r="N6">
+      <c r="Q6">
         <v>24.0838</v>
       </c>
-      <c r="O6">
+      <c r="R6">
         <v>0.93279999999999996</v>
       </c>
+      <c r="S6">
+        <v>0.30643799999999999</v>
+      </c>
+      <c r="T6">
+        <v>5.1365999999999996</v>
+      </c>
+      <c r="U6">
+        <v>0.55859999999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -684,81 +786,145 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7">
         <v>8</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>20</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>2</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7">
+        <v>798418</v>
+      </c>
+      <c r="M7" t="s">
         <v>15</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>300000</v>
       </c>
-      <c r="L7" t="s">
+      <c r="O7" t="s">
         <v>21</v>
       </c>
-      <c r="M7">
+      <c r="P7">
         <v>9.0899999999999998E-4</v>
       </c>
-      <c r="N7">
+      <c r="Q7">
         <v>30.412199999999999</v>
       </c>
-      <c r="O7">
+      <c r="R7">
         <v>0.97929999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8">
+        <v>37</v>
+      </c>
+      <c r="E8">
+        <v>49152</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>798418</v>
+      </c>
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8">
+        <v>300000</v>
+      </c>
+      <c r="O8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8">
+        <v>5.3600000000000002E-4</v>
+      </c>
+      <c r="Q8">
+        <v>32.706800000000001</v>
+      </c>
+      <c r="R8">
+        <v>0.98519999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>49152</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9">
         <v>16</v>
       </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8">
+      <c r="I9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9">
         <v>2</v>
       </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
+      <c r="K9">
+        <v>1727518</v>
+      </c>
+      <c r="M9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9">
+        <v>300000</v>
+      </c>
+      <c r="O9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9">
+        <v>4.35E-4</v>
+      </c>
+      <c r="Q9">
+        <v>33.615400000000001</v>
+      </c>
+      <c r="R9">
+        <v>0.98750000000000004</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="Q1:S1"/>
+  <mergeCells count="4">
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="S1:U1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
